--- a/repair/back/doc/estimate/program-periodic1.xlsx
+++ b/repair/back/doc/estimate/program-periodic1.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="Polaris Office Sheet" lastEdited="7" lowestEdited="7" rupBuild=""/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="30" windowWidth="25755" windowHeight="11595" activeTab="0"/>
+    <workbookView xWindow="360" yWindow="30" windowWidth="25755" windowHeight="11595" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="갑지" sheetId="1" r:id="rId1"/>
@@ -1379,7 +1379,7 @@
     <numFmt numFmtId="243" formatCode="_-&quot;₩&quot;* #,##0.00_-;&quot;₩&quot;&quot;₩&quot;\-&quot;₩&quot;* #,##0.00_-;_-&quot;₩&quot;* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="244" formatCode="&quot;₩&quot;#,##0.00;&quot;₩&quot;&quot;₩&quot;&quot;₩&quot;&quot;₩&quot;\-#,##0.00"/>
   </numFmts>
-  <fonts count="136">
+  <fonts count="144">
     <font>
       <sz val="10.0"/>
       <name val="바탕"/>
@@ -2112,6 +2112,52 @@
       <sz val="12.0"/>
       <name val="맑은 고딕"/>
       <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="11.0"/>
+      <name val="맑은 고딕"/>
+      <color theme="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14.0"/>
+      <name val="맑은 고딕"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11.0"/>
+      <name val="맑은 고딕"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11.0"/>
+      <name val="맑은 고딕"/>
+      <color theme="1"/>
+    </font>
+    <font>
+      <sz val="11.0"/>
+      <name val="맑은 고딕"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="13.0"/>
+      <name val="맑은 고딕"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <b/>
+      <u/>
+      <sz val="20.0"/>
+      <name val="맑은 고딕"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12.0"/>
+      <name val="맑은 고딕"/>
+      <color theme="1"/>
     </font>
   </fonts>
   <fills count="41">
@@ -17501,7 +17547,7 @@
     <col min="35" max="261" width="8.86214243" customWidth="1" outlineLevel="0"/>
   </cols>
   <sheetData>
-    <row r="1" spans="6:37" s="2" customFormat="1" ht="42.000000" customHeight="1">
+    <row r="1" spans="6:34" s="2" customFormat="1" ht="42.000000" customHeight="1">
       <c r="F1" s="227" t="s">
         <v>0</v>
       </c>
@@ -17534,7 +17580,7 @@
       <c r="AG1" s="227"/>
       <c r="AH1" s="1"/>
     </row>
-    <row r="2" spans="6:37" s="2" customFormat="1" ht="12.000000" customHeight="1">
+    <row r="2" spans="6:34" s="2" customFormat="1" ht="12.000000" customHeight="1">
       <c r="F2" s="111"/>
       <c r="G2" s="111"/>
       <c r="H2" s="111"/>
@@ -17565,7 +17611,7 @@
       <c r="AG2" s="112"/>
       <c r="AH2" s="1"/>
     </row>
-    <row r="3" spans="6:37" s="2" customFormat="1" ht="18.000000" customHeight="1">
+    <row r="3" spans="6:34" s="2" customFormat="1" ht="18.000000" customHeight="1">
       <c r="F3" s="219" t="s">
         <v>114</v>
       </c>
@@ -17598,7 +17644,7 @@
       <c r="AG3" s="219"/>
       <c r="AH3" s="109"/>
     </row>
-    <row r="4" spans="6:37" s="2" customFormat="1" ht="7.500000" customHeight="1">
+    <row r="4" spans="6:34" s="2" customFormat="1" ht="7.500000" customHeight="1">
       <c r="F4" s="113"/>
       <c r="G4" s="113"/>
       <c r="H4" s="113"/>
@@ -17629,7 +17675,7 @@
       <c r="AG4" s="114"/>
       <c r="AH4" s="1"/>
     </row>
-    <row r="5" spans="6:37" s="2" customFormat="1" ht="8.250000" customHeight="1">
+    <row r="5" spans="6:34" s="2" customFormat="1" ht="8.250000" customHeight="1">
       <c r="F5" s="111"/>
       <c r="G5" s="111"/>
       <c r="H5" s="111"/>
@@ -17660,7 +17706,7 @@
       <c r="AG5" s="112"/>
       <c r="AH5" s="1"/>
     </row>
-    <row r="6" spans="6:37" s="2" customFormat="1" ht="23.250000" customHeight="1">
+    <row r="6" spans="6:34" s="2" customFormat="1" ht="23.250000" customHeight="1">
       <c r="F6" s="224" t="s">
         <v>1</v>
       </c>
@@ -17695,7 +17741,7 @@
       <c r="AG6" s="111"/>
       <c r="AH6" s="1"/>
     </row>
-    <row r="7" spans="6:37" s="2" customFormat="1" ht="23.250000" customHeight="1">
+    <row r="7" spans="6:34" s="2" customFormat="1" ht="23.250000" customHeight="1">
       <c r="F7" s="224" t="s">
         <v>2</v>
       </c>
@@ -17730,7 +17776,7 @@
       <c r="AG7" s="111"/>
       <c r="AH7" s="1"/>
     </row>
-    <row r="8" spans="6:37" s="2" customFormat="1" ht="23.250000" customHeight="1">
+    <row r="8" spans="6:34" s="2" customFormat="1" ht="23.250000" customHeight="1">
       <c r="F8" s="224" t="s">
         <v>3</v>
       </c>
@@ -17765,7 +17811,7 @@
       <c r="AG8" s="111"/>
       <c r="AH8" s="1"/>
     </row>
-    <row r="9" spans="6:37" s="2" customFormat="1" ht="23.250000" customHeight="1">
+    <row r="9" spans="6:34" s="2" customFormat="1" ht="23.250000" customHeight="1">
       <c r="F9" s="224" t="s">
         <v>4</v>
       </c>
@@ -17778,32 +17824,8 @@
       <c r="K9" s="111"/>
       <c r="L9" s="111"/>
       <c r="M9" s="111"/>
-      <c r="N9" s="2"/>
-      <c r="O9" s="2"/>
-      <c r="P9" s="2"/>
-      <c r="Q9" s="2"/>
-      <c r="R9" s="2"/>
-      <c r="S9" s="2"/>
-      <c r="T9" s="2"/>
-      <c r="U9" s="2"/>
-      <c r="V9" s="2"/>
-      <c r="W9" s="2"/>
-      <c r="X9" s="2"/>
-      <c r="Y9" s="2"/>
-      <c r="Z9" s="2"/>
-      <c r="AA9" s="2"/>
-      <c r="AB9" s="2"/>
-      <c r="AC9" s="2"/>
-      <c r="AD9" s="2"/>
-      <c r="AE9" s="2"/>
-      <c r="AF9" s="2"/>
-      <c r="AG9" s="2"/>
-      <c r="AH9" s="2"/>
-      <c r="AI9" s="2"/>
-      <c r="AJ9" s="2"/>
-      <c r="AK9" s="2"/>
-    </row>
-    <row r="10" spans="6:37" s="2" customFormat="1" ht="23.250000" customHeight="1">
+    </row>
+    <row r="10" spans="6:34" s="2" customFormat="1" ht="23.250000" customHeight="1">
       <c r="F10" s="224" t="s">
         <v>6</v>
       </c>
@@ -17838,7 +17860,7 @@
       <c r="AG10" s="220"/>
       <c r="AH10" s="1"/>
     </row>
-    <row r="11" spans="6:37" s="2" customFormat="1" ht="7.500000" customHeight="1">
+    <row r="11" spans="6:34" s="2" customFormat="1" ht="7.500000" customHeight="1">
       <c r="F11" s="113"/>
       <c r="G11" s="113"/>
       <c r="H11" s="113"/>
@@ -17869,7 +17891,7 @@
       <c r="AG11" s="114"/>
       <c r="AH11" s="1"/>
     </row>
-    <row r="12" spans="6:37" s="2" customFormat="1" ht="13.500000" customHeight="1">
+    <row r="12" spans="6:34" s="2" customFormat="1" ht="13.500000" customHeight="1">
       <c r="F12" s="111"/>
       <c r="G12" s="111"/>
       <c r="H12" s="111"/>
@@ -17900,7 +17922,7 @@
       <c r="AG12" s="112"/>
       <c r="AH12" s="1"/>
     </row>
-    <row r="13" spans="6:37" s="2" customFormat="1" ht="19.500000" customHeight="1">
+    <row r="13" spans="6:34" s="2" customFormat="1" ht="19.500000" customHeight="1">
       <c r="F13" s="220" t="s">
         <v>182</v>
       </c>
@@ -17933,7 +17955,7 @@
       <c r="AG13" s="220"/>
       <c r="AH13" s="1"/>
     </row>
-    <row r="14" spans="6:37" s="2" customFormat="1" ht="9.750000" customHeight="1">
+    <row r="14" spans="6:34" s="2" customFormat="1" ht="9.750000" customHeight="1">
       <c r="F14" s="111"/>
       <c r="G14" s="111"/>
       <c r="H14" s="111"/>
@@ -17964,7 +17986,7 @@
       <c r="AG14" s="111"/>
       <c r="AH14" s="1"/>
     </row>
-    <row r="15" spans="6:37" s="2" customFormat="1" ht="65.250000" customHeight="1">
+    <row r="15" spans="6:34" s="2" customFormat="1" ht="65.250000" customHeight="1">
       <c r="F15" s="230" t="s">
         <v>183</v>
       </c>
@@ -17997,7 +18019,7 @@
       <c r="AG15" s="230"/>
       <c r="AH15" s="1"/>
     </row>
-    <row r="16" spans="6:37" s="2" customFormat="1" ht="9.750000" customHeight="1">
+    <row r="16" spans="6:34" s="2" customFormat="1" ht="9.750000" customHeight="1">
       <c r="F16" s="111"/>
       <c r="G16" s="111"/>
       <c r="H16" s="111"/>
@@ -19697,10 +19719,10 @@
     <mergeCell ref="J20:O20"/>
     <mergeCell ref="P20:AG20"/>
     <mergeCell ref="AM20:BH20"/>
+    <mergeCell ref="J21:O21"/>
+    <mergeCell ref="P21:AG21"/>
     <mergeCell ref="J22:O22"/>
     <mergeCell ref="P22:AG22"/>
-    <mergeCell ref="J21:O21"/>
-    <mergeCell ref="P21:AG21"/>
     <mergeCell ref="J23:O23"/>
     <mergeCell ref="P23:AG23"/>
     <mergeCell ref="J24:O24"/>
@@ -21842,7 +21864,7 @@
     </row>
     <row r="67" spans="5:24" ht="20.000000" customHeight="1">
       <c r="F67" s="103" t="str">
-        <f>"② 위      치 : "&amp;H54</f>
+        <f>"② 위      치 : "&amp;갑지!P21</f>
         <v>② 위      치 : 서울 성북구 길음로9길 50 (길음동)</v>
       </c>
       <c r="G67" s="103"/>
